--- a/test.xlsx
+++ b/test.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Potentiostatic EIS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ECSA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:J155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,39 +464,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>D:\!UNI\!sci_materials\!doktorat\artykuly_konferencje_projekty\!ARTYKULY\DONE\pentlandites_S8_vs_S4\Do_analizy\EIS\PASTYLKI\8. Ch4_161_Ch7s_2.1\EIS_POTENTIAL_#1_#6.DTA</t>
+          <t>D:\!UNI\!sci_materials\!doktorat\!wyniki\!TM3Se4\seria_3\CATALYSIS\PELLETS\SERIA_2\F2N_PELLET_STRONA_2_POMIAR_1_AM_REDOXME_01_07_2025\CV_ECSA_#1_#2.DTA</t>
         </is>
       </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>D:\!UNI\!sci_materials\!doktorat\artykuly_konferencje_projekty\!ARTYKULY\DONE\pentlandites_S8_vs_S4\Do_analizy\EIS\PASTYLKI\8. Ch4_161_Ch7s_2.1\EIS_POTENTIAL_#2_#6.DTA</t>
-        </is>
-      </c>
+      <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E vs RHE [V]</t>
+          <t>Curve number</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>Curve 0</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>Curve 1</t>
         </is>
       </c>
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Curve 2</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -506,32 +512,47 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Freq [Hz]</t>
+          <t>E vs RHE [V]</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Zreal [Ohm]</t>
+          <t>I [A]</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>-Zimag [Ohm]</t>
+          <t>J_GEO [A/cm2]</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Freq [Hz]</t>
+          <t>E vs RHE [V]</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Zreal [Ohm]</t>
+          <t>I [A]</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>-Zimag [Ohm]</t>
+          <t>J_GEO [A/cm2]</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>E vs RHE [V]</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>I [A]</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>J_GEO [A/cm2]</t>
         </is>
       </c>
     </row>
@@ -540,22 +561,31 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>100019.5</v>
+        <v>0.224874</v>
       </c>
       <c r="C5" t="n">
-        <v>13.97269</v>
+        <v>-6.87238e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07577159999999999</v>
+        <v>-6.87238e-06</v>
       </c>
       <c r="E5" t="n">
-        <v>100019.5</v>
+        <v>0.225864</v>
       </c>
       <c r="F5" t="n">
-        <v>13.72269</v>
+        <v>-6.62784e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0404452</v>
+        <v>-6.62784e-06</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.225873</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-6.68711e-06</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-6.68711e-06</v>
       </c>
     </row>
     <row r="6">
@@ -563,22 +593,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>79511.72</v>
+        <v>0.225851</v>
       </c>
       <c r="C6" t="n">
-        <v>14.04569</v>
+        <v>-6.33313e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0442784</v>
+        <v>-6.33313e-06</v>
       </c>
       <c r="E6" t="n">
-        <v>79511.72</v>
+        <v>0.226855</v>
       </c>
       <c r="F6" t="n">
-        <v>13.70918</v>
+        <v>-6.4091e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009213600000000001</v>
+        <v>-6.4091e-06</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.22686</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-6.47197e-06</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-6.47197e-06</v>
       </c>
     </row>
     <row r="7">
@@ -586,22 +625,31 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>63105.47</v>
+        <v>0.226863</v>
       </c>
       <c r="C7" t="n">
-        <v>13.9192</v>
+        <v>-6.12322e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0968238</v>
+        <v>-6.12322e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>63105.47</v>
+        <v>0.227867</v>
       </c>
       <c r="F7" t="n">
-        <v>13.69209</v>
+        <v>-6.22504e-06</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0565186</v>
+        <v>-6.22504e-06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.227887</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-6.28163e-06</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-6.28163e-06</v>
       </c>
     </row>
     <row r="8">
@@ -609,22 +657,31 @@
         <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>50214.84</v>
+        <v>0.227878</v>
       </c>
       <c r="C8" t="n">
-        <v>13.99049</v>
+        <v>-5.95287e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1034339</v>
+        <v>-5.95287e-06</v>
       </c>
       <c r="E8" t="n">
-        <v>50214.84</v>
+        <v>0.228871</v>
       </c>
       <c r="F8" t="n">
-        <v>13.75242</v>
+        <v>-6.04589e-06</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0629946</v>
+        <v>-6.04589e-06</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.228885</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-6.10794e-06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-6.10794e-06</v>
       </c>
     </row>
     <row r="9">
@@ -632,22 +689,31 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>39902.34</v>
+        <v>0.228879</v>
       </c>
       <c r="C9" t="n">
-        <v>13.98909</v>
+        <v>-5.78312e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>0.113139</v>
+        <v>-5.78312e-06</v>
       </c>
       <c r="E9" t="n">
-        <v>39902.34</v>
+        <v>0.229869</v>
       </c>
       <c r="F9" t="n">
-        <v>13.67034</v>
+        <v>-5.88347e-06</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0667695</v>
+        <v>-5.88347e-06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.229868</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-5.94585e-06</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-5.94585e-06</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +721,31 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>31699.22</v>
+        <v>0.229859</v>
       </c>
       <c r="C10" t="n">
-        <v>14.08373</v>
+        <v>-5.63363e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1196965</v>
+        <v>-5.63363e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>31699.22</v>
+        <v>0.230887</v>
       </c>
       <c r="F10" t="n">
-        <v>13.71951</v>
+        <v>-5.72153e-06</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07112599999999999</v>
+        <v>-5.72153e-06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.23088</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-5.78918e-06</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-5.78918e-06</v>
       </c>
     </row>
     <row r="11">
@@ -678,22 +753,31 @@
         <v>6</v>
       </c>
       <c r="B11" t="n">
-        <v>25136.72</v>
+        <v>0.230874</v>
       </c>
       <c r="C11" t="n">
-        <v>14.17363</v>
+        <v>-5.47918e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1279134</v>
+        <v>-5.47918e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>25136.72</v>
+        <v>0.231882</v>
       </c>
       <c r="F11" t="n">
-        <v>13.79768</v>
+        <v>-5.57497e-06</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0753229</v>
+        <v>-5.57497e-06</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.231884</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-5.63333e-06</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-5.63333e-06</v>
       </c>
     </row>
     <row r="12">
@@ -701,22 +785,31 @@
         <v>7</v>
       </c>
       <c r="B12" t="n">
-        <v>19980.47</v>
+        <v>0.231875</v>
       </c>
       <c r="C12" t="n">
-        <v>13.99958</v>
+        <v>-5.33515e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1349589</v>
+        <v>-5.33515e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>19980.47</v>
+        <v>0.232882</v>
       </c>
       <c r="F12" t="n">
-        <v>13.76586</v>
+        <v>-5.41516e-06</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0779281</v>
+        <v>-5.41516e-06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.232874</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-5.47759e-06</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-5.47759e-06</v>
       </c>
     </row>
     <row r="13">
@@ -724,22 +817,31 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>15878.91</v>
+        <v>0.232878</v>
       </c>
       <c r="C13" t="n">
-        <v>14.10924</v>
+        <v>-5.18906e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1405898</v>
+        <v>-5.18906e-06</v>
       </c>
       <c r="E13" t="n">
-        <v>15878.91</v>
+        <v>0.233882</v>
       </c>
       <c r="F13" t="n">
-        <v>13.71451</v>
+        <v>-5.27635e-06</v>
       </c>
       <c r="G13" t="n">
-        <v>0.07783229999999999</v>
+        <v>-5.27635e-06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.233865</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-5.33408e-06</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-5.33408e-06</v>
       </c>
     </row>
     <row r="14">
@@ -747,22 +849,31 @@
         <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>12597.66</v>
+        <v>0.233873</v>
       </c>
       <c r="C14" t="n">
-        <v>14.2145</v>
+        <v>-5.05233e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1472733</v>
+        <v>-5.05233e-06</v>
       </c>
       <c r="E14" t="n">
-        <v>12597.66</v>
+        <v>0.234876</v>
       </c>
       <c r="F14" t="n">
-        <v>13.85062</v>
+        <v>-5.13244e-06</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0808408</v>
+        <v>-5.13244e-06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.234871</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-5.19029e-06</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-5.19029e-06</v>
       </c>
     </row>
     <row r="15">
@@ -770,22 +881,31 @@
         <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>10019.53</v>
+        <v>0.234873</v>
       </c>
       <c r="C15" t="n">
-        <v>14.32566</v>
+        <v>-4.9067e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1548154</v>
+        <v>-4.9067e-06</v>
       </c>
       <c r="E15" t="n">
-        <v>10019.53</v>
+        <v>0.235879</v>
       </c>
       <c r="F15" t="n">
-        <v>13.76697</v>
+        <v>-4.99747e-06</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08331379999999999</v>
+        <v>-4.99747e-06</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.235871</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-5.05227e-06</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-5.05227e-06</v>
       </c>
     </row>
     <row r="16">
@@ -793,22 +913,31 @@
         <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>7928.241</v>
+        <v>0.235868</v>
       </c>
       <c r="C16" t="n">
-        <v>14.21046</v>
+        <v>-4.77578e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1616911</v>
+        <v>-4.77578e-06</v>
       </c>
       <c r="E16" t="n">
-        <v>7928.241</v>
+        <v>0.236886</v>
       </c>
       <c r="F16" t="n">
-        <v>13.78199</v>
+        <v>-4.85887e-06</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0863907</v>
+        <v>-4.85887e-06</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.23688</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-4.91452e-06</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4.91452e-06</v>
       </c>
     </row>
     <row r="17">
@@ -816,22 +945,31 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>6307.871</v>
+        <v>0.236882</v>
       </c>
       <c r="C17" t="n">
-        <v>14.15805</v>
+        <v>-4.63826e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1736638</v>
+        <v>-4.63826e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>6307.871</v>
+        <v>0.237879</v>
       </c>
       <c r="F17" t="n">
-        <v>13.80322</v>
+        <v>-4.7286e-06</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0901681</v>
+        <v>-4.7286e-06</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.237872</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4.78408e-06</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-4.78408e-06</v>
       </c>
     </row>
     <row r="18">
@@ -839,22 +977,31 @@
         <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>5034.722</v>
+        <v>0.237873</v>
       </c>
       <c r="C18" t="n">
-        <v>14.28467</v>
+        <v>-4.52061e-06</v>
       </c>
       <c r="D18" t="n">
-        <v>0.181866</v>
+        <v>-4.52061e-06</v>
       </c>
       <c r="E18" t="n">
-        <v>5034.722</v>
+        <v>0.23887</v>
       </c>
       <c r="F18" t="n">
-        <v>13.97032</v>
+        <v>-4.59532e-06</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0947465</v>
+        <v>-4.59532e-06</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.238866</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4.6571e-06</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-4.6571e-06</v>
       </c>
     </row>
     <row r="19">
@@ -862,22 +1009,31 @@
         <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>3993.056</v>
+        <v>0.238867</v>
       </c>
       <c r="C19" t="n">
-        <v>14.43605</v>
+        <v>-4.38743e-06</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1963963</v>
+        <v>-4.38743e-06</v>
       </c>
       <c r="E19" t="n">
-        <v>3993.056</v>
+        <v>0.239861</v>
       </c>
       <c r="F19" t="n">
-        <v>13.75934</v>
+        <v>-4.47423e-06</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0988082</v>
+        <v>-4.47423e-06</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.239871</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4.52879e-06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-4.52879e-06</v>
       </c>
     </row>
     <row r="20">
@@ -885,22 +1041,31 @@
         <v>15</v>
       </c>
       <c r="B20" t="n">
-        <v>3144.055</v>
+        <v>0.239881</v>
       </c>
       <c r="C20" t="n">
-        <v>14.54482</v>
+        <v>-4.26956e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2101679</v>
+        <v>-4.26956e-06</v>
       </c>
       <c r="E20" t="n">
-        <v>3144.055</v>
+        <v>0.240844</v>
       </c>
       <c r="F20" t="n">
-        <v>13.83589</v>
+        <v>-4.33954e-06</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1047056</v>
+        <v>-4.33954e-06</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4.39932e-06</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-4.39932e-06</v>
       </c>
     </row>
     <row r="21">
@@ -908,22 +1073,31 @@
         <v>16</v>
       </c>
       <c r="B21" t="n">
-        <v>2519.531</v>
+        <v>0.24086</v>
       </c>
       <c r="C21" t="n">
-        <v>14.42734</v>
+        <v>-4.14919e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2229651</v>
+        <v>-4.14919e-06</v>
       </c>
       <c r="E21" t="n">
-        <v>2519.531</v>
+        <v>0.241864</v>
       </c>
       <c r="F21" t="n">
-        <v>13.84743</v>
+        <v>-4.22209e-06</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1123331</v>
+        <v>-4.22209e-06</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.241874</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-4.28041e-06</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-4.28041e-06</v>
       </c>
     </row>
     <row r="22">
@@ -931,22 +1105,31 @@
         <v>17</v>
       </c>
       <c r="B22" t="n">
-        <v>2000.762</v>
+        <v>0.241865</v>
       </c>
       <c r="C22" t="n">
-        <v>14.54335</v>
+        <v>-4.03856e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2392452</v>
+        <v>-4.03856e-06</v>
       </c>
       <c r="E22" t="n">
-        <v>2000.762</v>
+        <v>0.242868</v>
       </c>
       <c r="F22" t="n">
-        <v>13.86723</v>
+        <v>-4.09838e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1194577</v>
+        <v>-4.09838e-06</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.24289</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-4.16499e-06</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-4.16499e-06</v>
       </c>
     </row>
     <row r="23">
@@ -954,22 +1137,31 @@
         <v>18</v>
       </c>
       <c r="B23" t="n">
-        <v>1580.669</v>
+        <v>0.242877</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28437</v>
+        <v>-3.9172e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2573629</v>
+        <v>-3.9172e-06</v>
       </c>
       <c r="E23" t="n">
-        <v>1580.669</v>
+        <v>0.243876</v>
       </c>
       <c r="F23" t="n">
-        <v>13.85092</v>
+        <v>-3.98847e-06</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1301694</v>
+        <v>-3.98847e-06</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.243883</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-4.04812e-06</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-4.04812e-06</v>
       </c>
     </row>
     <row r="24">
@@ -977,22 +1169,31 @@
         <v>19</v>
       </c>
       <c r="B24" t="n">
-        <v>1253.634</v>
+        <v>0.243874</v>
       </c>
       <c r="C24" t="n">
-        <v>14.26195</v>
+        <v>-3.8122e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2768152</v>
+        <v>-3.8122e-06</v>
       </c>
       <c r="E24" t="n">
-        <v>1253.634</v>
+        <v>0.244867</v>
       </c>
       <c r="F24" t="n">
-        <v>13.91794</v>
+        <v>-3.8747e-06</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1409484</v>
+        <v>-3.8747e-06</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.244874</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-3.92929e-06</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.92929e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1000,22 +1201,31 @@
         <v>20</v>
       </c>
       <c r="B25" t="n">
-        <v>1000.702</v>
+        <v>0.24487</v>
       </c>
       <c r="C25" t="n">
-        <v>14.44271</v>
+        <v>-3.69446e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3007418</v>
+        <v>-3.69446e-06</v>
       </c>
       <c r="E25" t="n">
-        <v>1000.702</v>
+        <v>0.245864</v>
       </c>
       <c r="F25" t="n">
-        <v>13.90583</v>
+        <v>-3.76761e-06</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1560543</v>
+        <v>-3.76761e-06</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.245871</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-3.81773e-06</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-3.81773e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1023,22 +1233,31 @@
         <v>21</v>
       </c>
       <c r="B26" t="n">
-        <v>790.0281</v>
+        <v>0.245867</v>
       </c>
       <c r="C26" t="n">
-        <v>14.57714</v>
+        <v>-3.58962e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>0.32833</v>
+        <v>-3.58962e-06</v>
       </c>
       <c r="E26" t="n">
-        <v>790.0281</v>
+        <v>0.246872</v>
       </c>
       <c r="F26" t="n">
-        <v>13.93264</v>
+        <v>-3.64742e-06</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1723051</v>
+        <v>-3.64742e-06</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.246865</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3.70597e-06</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-3.70597e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1046,22 +1265,31 @@
         <v>22</v>
       </c>
       <c r="B27" t="n">
-        <v>628.811</v>
+        <v>0.24687</v>
       </c>
       <c r="C27" t="n">
-        <v>14.73625</v>
+        <v>-3.47747e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3620622</v>
+        <v>-3.47747e-06</v>
       </c>
       <c r="E27" t="n">
-        <v>628.811</v>
+        <v>0.247878</v>
       </c>
       <c r="F27" t="n">
-        <v>13.90851</v>
+        <v>-3.54469e-06</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1904934</v>
+        <v>-3.54469e-06</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.247865</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-3.59833e-06</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.59833e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1069,22 +1297,31 @@
         <v>23</v>
       </c>
       <c r="B28" t="n">
-        <v>502.2321</v>
+        <v>0.247875</v>
       </c>
       <c r="C28" t="n">
-        <v>14.52448</v>
+        <v>-3.38053e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3877392</v>
+        <v>-3.38053e-06</v>
       </c>
       <c r="E28" t="n">
-        <v>502.2321</v>
+        <v>0.248878</v>
       </c>
       <c r="F28" t="n">
-        <v>13.87828</v>
+        <v>-3.43276e-06</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2088495</v>
+        <v>-3.43276e-06</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.248864</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-3.49348e-06</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3.49348e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1092,22 +1329,31 @@
         <v>24</v>
       </c>
       <c r="B29" t="n">
-        <v>400.1524</v>
+        <v>0.248878</v>
       </c>
       <c r="C29" t="n">
-        <v>14.69712</v>
+        <v>-3.27199e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4210321</v>
+        <v>-3.27199e-06</v>
       </c>
       <c r="E29" t="n">
-        <v>400.1524</v>
+        <v>0.249886</v>
       </c>
       <c r="F29" t="n">
-        <v>13.93616</v>
+        <v>-3.33834e-06</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2336901</v>
+        <v>-3.33834e-06</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.249871</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-3.39237e-06</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-3.39237e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1115,22 +1361,31 @@
         <v>25</v>
       </c>
       <c r="B30" t="n">
-        <v>315.5048</v>
+        <v>0.249881</v>
       </c>
       <c r="C30" t="n">
-        <v>14.86409</v>
+        <v>-3.18161e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4640879</v>
+        <v>-3.18161e-06</v>
       </c>
       <c r="E30" t="n">
-        <v>315.5048</v>
+        <v>0.250886</v>
       </c>
       <c r="F30" t="n">
-        <v>13.97032</v>
+        <v>-3.22577e-06</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2619383</v>
+        <v>-3.22577e-06</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.250865</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-3.29073e-06</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-3.29073e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1138,22 +1393,31 @@
         <v>26</v>
       </c>
       <c r="B31" t="n">
-        <v>252.0161</v>
+        <v>0.250882</v>
       </c>
       <c r="C31" t="n">
-        <v>14.8864</v>
+        <v>-3.07474e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5047079</v>
+        <v>-3.07474e-06</v>
       </c>
       <c r="E31" t="n">
-        <v>252.0161</v>
+        <v>0.251868</v>
       </c>
       <c r="F31" t="n">
-        <v>14.07289</v>
+        <v>-3.13644e-06</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2937948</v>
+        <v>-3.13644e-06</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.25185</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-3.19077e-06</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-3.19077e-06</v>
       </c>
     </row>
     <row r="32">
@@ -1161,22 +1425,31 @@
         <v>27</v>
       </c>
       <c r="B32" t="n">
-        <v>200.3205</v>
+        <v>0.251865</v>
       </c>
       <c r="C32" t="n">
-        <v>14.87167</v>
+        <v>-2.98462e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5594249</v>
+        <v>-2.98462e-06</v>
       </c>
       <c r="E32" t="n">
-        <v>200.3205</v>
+        <v>0.252896</v>
       </c>
       <c r="F32" t="n">
-        <v>14.03054</v>
+        <v>-3.03255e-06</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3281205</v>
+        <v>-3.03255e-06</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.252887</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-3.09212e-06</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-3.09212e-06</v>
       </c>
     </row>
     <row r="33">
@@ -1184,22 +1457,31 @@
         <v>28</v>
       </c>
       <c r="B33" t="n">
-        <v>158.0056</v>
+        <v>0.252883</v>
       </c>
       <c r="C33" t="n">
-        <v>14.92423</v>
+        <v>-2.88493e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6085413</v>
+        <v>-2.88493e-06</v>
       </c>
       <c r="E33" t="n">
-        <v>158.0056</v>
+        <v>0.2539</v>
       </c>
       <c r="F33" t="n">
-        <v>14.10624</v>
+        <v>-2.94294e-06</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3733726</v>
+        <v>-2.94294e-06</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.253891</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-2.99576e-06</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-2.99576e-06</v>
       </c>
     </row>
     <row r="34">
@@ -1207,22 +1489,31 @@
         <v>29</v>
       </c>
       <c r="B34" t="n">
-        <v>125.558</v>
+        <v>0.25388</v>
       </c>
       <c r="C34" t="n">
-        <v>15.11203</v>
+        <v>-2.79519e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6658236</v>
+        <v>-2.79519e-06</v>
       </c>
       <c r="E34" t="n">
-        <v>125.558</v>
+        <v>0.254884</v>
       </c>
       <c r="F34" t="n">
-        <v>14.06302</v>
+        <v>-2.84307e-06</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4183352</v>
+        <v>-2.84307e-06</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.254884</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-2.90285e-06</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-2.90285e-06</v>
       </c>
     </row>
     <row r="35">
@@ -1230,22 +1521,31 @@
         <v>30</v>
       </c>
       <c r="B35" t="n">
-        <v>99.73399999999999</v>
+        <v>0.254866</v>
       </c>
       <c r="C35" t="n">
-        <v>15.16378</v>
+        <v>-2.69566e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7310176</v>
+        <v>-2.69566e-06</v>
       </c>
       <c r="E35" t="n">
-        <v>99.73399999999999</v>
+        <v>0.255907</v>
       </c>
       <c r="F35" t="n">
-        <v>14.22266</v>
+        <v>-2.75321e-06</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4786802</v>
+        <v>-2.75321e-06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.255911</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2.81022e-06</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-2.81022e-06</v>
       </c>
     </row>
     <row r="36">
@@ -1253,22 +1553,31 @@
         <v>31</v>
       </c>
       <c r="B36" t="n">
-        <v>79.44915</v>
+        <v>0.255902</v>
       </c>
       <c r="C36" t="n">
-        <v>15.27474</v>
+        <v>-2.60774e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8005707</v>
+        <v>-2.60774e-06</v>
       </c>
       <c r="E36" t="n">
-        <v>79.44915</v>
+        <v>0.256883</v>
       </c>
       <c r="F36" t="n">
-        <v>14.26699</v>
+        <v>-2.65902e-06</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5331997000000001</v>
+        <v>-2.65902e-06</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.25689</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2.72168e-06</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-2.72168e-06</v>
       </c>
     </row>
     <row r="37">
@@ -1276,22 +1585,31 @@
         <v>32</v>
       </c>
       <c r="B37" t="n">
-        <v>62.91946</v>
+        <v>0.256878</v>
       </c>
       <c r="C37" t="n">
-        <v>15.36493</v>
+        <v>-2.51381e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8739401</v>
+        <v>-2.51381e-06</v>
       </c>
       <c r="E37" t="n">
-        <v>62.91946</v>
+        <v>0.257882</v>
       </c>
       <c r="F37" t="n">
-        <v>14.32088</v>
+        <v>-2.57357e-06</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6057357</v>
+        <v>-2.57357e-06</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.257883</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-2.62744e-06</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-2.62744e-06</v>
       </c>
     </row>
     <row r="38">
@@ -1299,22 +1617,31 @@
         <v>33</v>
       </c>
       <c r="B38" t="n">
-        <v>49.86702</v>
+        <v>0.257868</v>
       </c>
       <c r="C38" t="n">
-        <v>15.48204</v>
+        <v>-2.42869e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9440705</v>
+        <v>-2.42869e-06</v>
       </c>
       <c r="E38" t="n">
-        <v>49.86702</v>
+        <v>0.258886</v>
       </c>
       <c r="F38" t="n">
-        <v>14.43305</v>
+        <v>-2.48331e-06</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6737482</v>
+        <v>-2.48331e-06</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.25889</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-2.53056e-06</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-2.53056e-06</v>
       </c>
     </row>
     <row r="39">
@@ -1322,22 +1649,31 @@
         <v>34</v>
       </c>
       <c r="B39" t="n">
-        <v>38.42213</v>
+        <v>0.25888</v>
       </c>
       <c r="C39" t="n">
-        <v>15.78452</v>
+        <v>-2.33683e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>1.05208</v>
+        <v>-2.33683e-06</v>
       </c>
       <c r="E39" t="n">
-        <v>38.42213</v>
+        <v>0.25989</v>
       </c>
       <c r="F39" t="n">
-        <v>14.61662</v>
+        <v>-2.39792e-06</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7817397</v>
+        <v>-2.39792e-06</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.259896</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-2.44082e-06</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-2.44082e-06</v>
       </c>
     </row>
     <row r="40">
@@ -1345,22 +1681,31 @@
         <v>35</v>
       </c>
       <c r="B40" t="n">
-        <v>31.25</v>
+        <v>0.259885</v>
       </c>
       <c r="C40" t="n">
-        <v>16.02642</v>
+        <v>-2.25743e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>1.110308</v>
+        <v>-2.25743e-06</v>
       </c>
       <c r="E40" t="n">
-        <v>31.25</v>
+        <v>0.260889</v>
       </c>
       <c r="F40" t="n">
-        <v>14.61125</v>
+        <v>-2.30748e-06</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8585303</v>
+        <v>-2.30748e-06</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.260883</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-2.35902e-06</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-2.35902e-06</v>
       </c>
     </row>
     <row r="41">
@@ -1368,22 +1713,31 @@
         <v>36</v>
       </c>
       <c r="B41" t="n">
-        <v>24.93351</v>
+        <v>0.26089</v>
       </c>
       <c r="C41" t="n">
-        <v>16.14447</v>
+        <v>-2.17004e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>1.22458</v>
+        <v>-2.17004e-06</v>
       </c>
       <c r="E41" t="n">
-        <v>24.93351</v>
+        <v>0.261883</v>
       </c>
       <c r="F41" t="n">
-        <v>14.81953</v>
+        <v>-2.226e-06</v>
       </c>
       <c r="G41" t="n">
-        <v>0.957446</v>
+        <v>-2.226e-06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.261897</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-2.27366e-06</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-2.27366e-06</v>
       </c>
     </row>
     <row r="42">
@@ -1391,22 +1745,31 @@
         <v>37</v>
       </c>
       <c r="B42" t="n">
-        <v>20.03205</v>
+        <v>0.261888</v>
       </c>
       <c r="C42" t="n">
-        <v>16.28337</v>
+        <v>-2.09814e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.298215</v>
+        <v>-2.09814e-06</v>
       </c>
       <c r="E42" t="n">
-        <v>20.03205</v>
+        <v>0.262878</v>
       </c>
       <c r="F42" t="n">
-        <v>14.9701</v>
+        <v>-2.14694e-06</v>
       </c>
       <c r="G42" t="n">
-        <v>1.086454</v>
+        <v>-2.14694e-06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.262888</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-2.19665e-06</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-2.19665e-06</v>
       </c>
     </row>
     <row r="43">
@@ -1414,22 +1777,31 @@
         <v>38</v>
       </c>
       <c r="B43" t="n">
-        <v>15.625</v>
+        <v>0.262884</v>
       </c>
       <c r="C43" t="n">
-        <v>16.28837</v>
+        <v>-2.01706e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>1.410169</v>
+        <v>-2.01706e-06</v>
       </c>
       <c r="E43" t="n">
-        <v>15.625</v>
+        <v>0.263869</v>
       </c>
       <c r="F43" t="n">
-        <v>15.09608</v>
+        <v>-2.06327e-06</v>
       </c>
       <c r="G43" t="n">
-        <v>1.175293</v>
+        <v>-2.06327e-06</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.263878</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-2.1061e-06</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-2.1061e-06</v>
       </c>
     </row>
     <row r="44">
@@ -1437,22 +1809,31 @@
         <v>39</v>
       </c>
       <c r="B44" t="n">
-        <v>12.46675</v>
+        <v>0.263881</v>
       </c>
       <c r="C44" t="n">
-        <v>16.71714</v>
+        <v>-1.93731e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>1.506522</v>
+        <v>-1.93731e-06</v>
       </c>
       <c r="E44" t="n">
-        <v>12.46675</v>
+        <v>0.264878</v>
       </c>
       <c r="F44" t="n">
-        <v>15.32262</v>
+        <v>-1.9794e-06</v>
       </c>
       <c r="G44" t="n">
-        <v>1.312666</v>
+        <v>-1.9794e-06</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.264876</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2.02788e-06</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-2.02788e-06</v>
       </c>
     </row>
     <row r="45">
@@ -1460,22 +1841,31 @@
         <v>40</v>
       </c>
       <c r="B45" t="n">
-        <v>9.9734</v>
+        <v>0.264883</v>
       </c>
       <c r="C45" t="n">
-        <v>16.95481</v>
+        <v>-1.85439e-06</v>
       </c>
       <c r="D45" t="n">
-        <v>1.636349</v>
+        <v>-1.85439e-06</v>
       </c>
       <c r="E45" t="n">
-        <v>9.9734</v>
+        <v>0.265887</v>
       </c>
       <c r="F45" t="n">
-        <v>15.38433</v>
+        <v>-1.90852e-06</v>
       </c>
       <c r="G45" t="n">
-        <v>1.319113</v>
+        <v>-1.90852e-06</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.265875</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-1.94826e-06</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-1.94826e-06</v>
       </c>
     </row>
     <row r="46">
@@ -1483,22 +1873,31 @@
         <v>41</v>
       </c>
       <c r="B46" t="n">
-        <v>7.971939</v>
+        <v>0.265886</v>
       </c>
       <c r="C46" t="n">
-        <v>17.17884</v>
+        <v>-1.78327e-06</v>
       </c>
       <c r="D46" t="n">
-        <v>1.706322</v>
+        <v>-1.78327e-06</v>
       </c>
       <c r="E46" t="n">
-        <v>7.971939</v>
+        <v>0.266865</v>
       </c>
       <c r="F46" t="n">
-        <v>15.64776</v>
+        <v>-1.82575e-06</v>
       </c>
       <c r="G46" t="n">
-        <v>1.443406</v>
+        <v>-1.82575e-06</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.266864</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1.87223e-06</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-1.87223e-06</v>
       </c>
     </row>
     <row r="47">
@@ -1506,22 +1905,31 @@
         <v>42</v>
       </c>
       <c r="B47" t="n">
-        <v>6.351626</v>
+        <v>0.266869</v>
       </c>
       <c r="C47" t="n">
-        <v>17.53759</v>
+        <v>-1.70018e-06</v>
       </c>
       <c r="D47" t="n">
-        <v>1.784137</v>
+        <v>-1.70018e-06</v>
       </c>
       <c r="E47" t="n">
-        <v>6.351626</v>
+        <v>0.26786</v>
       </c>
       <c r="F47" t="n">
-        <v>15.90625</v>
+        <v>-1.75293e-06</v>
       </c>
       <c r="G47" t="n">
-        <v>1.542323</v>
+        <v>-1.75293e-06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1.79289e-06</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-1.79289e-06</v>
       </c>
     </row>
     <row r="48">
@@ -1529,22 +1937,31 @@
         <v>43</v>
       </c>
       <c r="B48" t="n">
-        <v>5.013369</v>
+        <v>0.267873</v>
       </c>
       <c r="C48" t="n">
-        <v>17.87069</v>
+        <v>-1.62737e-06</v>
       </c>
       <c r="D48" t="n">
-        <v>1.85514</v>
+        <v>-1.62737e-06</v>
       </c>
       <c r="E48" t="n">
-        <v>5.013369</v>
+        <v>0.268876</v>
       </c>
       <c r="F48" t="n">
-        <v>16.20169</v>
+        <v>-1.67426e-06</v>
       </c>
       <c r="G48" t="n">
-        <v>1.543398</v>
+        <v>-1.67426e-06</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.72071e-06</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-1.72071e-06</v>
       </c>
     </row>
     <row r="49">
@@ -1552,22 +1969,31 @@
         <v>44</v>
       </c>
       <c r="B49" t="n">
-        <v>3.985969</v>
+        <v>0.268894</v>
       </c>
       <c r="C49" t="n">
-        <v>18.06328</v>
+        <v>-1.54837e-06</v>
       </c>
       <c r="D49" t="n">
-        <v>1.798803</v>
+        <v>-1.54837e-06</v>
       </c>
       <c r="E49" t="n">
-        <v>3.985969</v>
+        <v>0.269883</v>
       </c>
       <c r="F49" t="n">
-        <v>16.53068</v>
+        <v>-1.59955e-06</v>
       </c>
       <c r="G49" t="n">
-        <v>1.700461</v>
+        <v>-1.59955e-06</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.269879</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-1.64426e-06</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-1.64426e-06</v>
       </c>
     </row>
     <row r="50">
@@ -1575,22 +2001,31 @@
         <v>45</v>
       </c>
       <c r="B50" t="n">
-        <v>3.175813</v>
+        <v>0.26989</v>
       </c>
       <c r="C50" t="n">
-        <v>18.35489</v>
+        <v>-1.47959e-06</v>
       </c>
       <c r="D50" t="n">
-        <v>1.899636</v>
+        <v>-1.47959e-06</v>
       </c>
       <c r="E50" t="n">
-        <v>3.175813</v>
+        <v>0.270877</v>
       </c>
       <c r="F50" t="n">
-        <v>16.86887</v>
+        <v>-1.52162e-06</v>
       </c>
       <c r="G50" t="n">
-        <v>1.607852</v>
+        <v>-1.52162e-06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.270867</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-1.56887e-06</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-1.56887e-06</v>
       </c>
     </row>
     <row r="51">
@@ -1598,22 +2033,31 @@
         <v>46</v>
       </c>
       <c r="B51" t="n">
-        <v>2.516103</v>
+        <v>0.27087</v>
       </c>
       <c r="C51" t="n">
-        <v>18.83588</v>
+        <v>-1.40347e-06</v>
       </c>
       <c r="D51" t="n">
-        <v>1.716151</v>
+        <v>-1.40347e-06</v>
       </c>
       <c r="E51" t="n">
-        <v>2.516103</v>
+        <v>0.271887</v>
       </c>
       <c r="F51" t="n">
-        <v>17.10254</v>
+        <v>-1.45752e-06</v>
       </c>
       <c r="G51" t="n">
-        <v>1.667514</v>
+        <v>-1.45752e-06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.271886</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-1.4911e-06</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-1.4911e-06</v>
       </c>
     </row>
     <row r="52">
@@ -1621,22 +2065,31 @@
         <v>47</v>
       </c>
       <c r="B52" t="n">
-        <v>1.99553</v>
+        <v>0.271885</v>
       </c>
       <c r="C52" t="n">
-        <v>19.12941</v>
+        <v>-1.33466e-06</v>
       </c>
       <c r="D52" t="n">
-        <v>1.968378</v>
+        <v>-1.33466e-06</v>
       </c>
       <c r="E52" t="n">
-        <v>1.99553</v>
+        <v>0.272886</v>
       </c>
       <c r="F52" t="n">
-        <v>17.47344</v>
+        <v>-1.37713e-06</v>
       </c>
       <c r="G52" t="n">
-        <v>1.457646</v>
+        <v>-1.37713e-06</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-1.41877e-06</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-1.41877e-06</v>
       </c>
     </row>
     <row r="53">
@@ -1644,22 +2097,31 @@
         <v>48</v>
       </c>
       <c r="B53" t="n">
-        <v>1.587906</v>
+        <v>0.27289</v>
       </c>
       <c r="C53" t="n">
-        <v>19.26938</v>
+        <v>-1.25756e-06</v>
       </c>
       <c r="D53" t="n">
-        <v>2.001371</v>
+        <v>-1.25756e-06</v>
       </c>
       <c r="E53" t="n">
-        <v>1.587906</v>
+        <v>0.273872</v>
       </c>
       <c r="F53" t="n">
-        <v>17.81799</v>
+        <v>-1.30743e-06</v>
       </c>
       <c r="G53" t="n">
-        <v>1.408764</v>
+        <v>-1.30743e-06</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.273876</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-1.34713e-06</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-1.34713e-06</v>
       </c>
     </row>
     <row r="54">
@@ -1667,22 +2129,31 @@
         <v>49</v>
       </c>
       <c r="B54" t="n">
-        <v>1.258052</v>
+        <v>0.273876</v>
       </c>
       <c r="C54" t="n">
-        <v>20.06946</v>
+        <v>-1.19687e-06</v>
       </c>
       <c r="D54" t="n">
-        <v>1.778587</v>
+        <v>-1.19687e-06</v>
       </c>
       <c r="E54" t="n">
-        <v>1.258052</v>
+        <v>0.274875</v>
       </c>
       <c r="F54" t="n">
-        <v>18.08121</v>
+        <v>-1.23226e-06</v>
       </c>
       <c r="G54" t="n">
-        <v>1.261242</v>
+        <v>-1.23226e-06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.274879</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-1.27987e-06</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-1.27987e-06</v>
       </c>
     </row>
     <row r="55">
@@ -1690,30 +2161,3227 @@
         <v>50</v>
       </c>
       <c r="B55" t="n">
-        <v>0.997765</v>
+        <v>0.274861</v>
       </c>
       <c r="C55" t="n">
-        <v>19.48406</v>
+        <v>-1.1218e-06</v>
       </c>
       <c r="D55" t="n">
-        <v>1.47409</v>
+        <v>-1.1218e-06</v>
       </c>
       <c r="E55" t="n">
-        <v>0.997765</v>
+        <v>0.275881</v>
       </c>
       <c r="F55" t="n">
-        <v>18.20408</v>
+        <v>-1.16577e-06</v>
       </c>
       <c r="G55" t="n">
-        <v>1.050688</v>
-      </c>
+        <v>-1.16577e-06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.275893</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-1.20696e-06</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-1.20696e-06</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0.275873</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.05662e-06</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.05662e-06</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.27688</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1.09201e-06</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-1.09201e-06</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.276885</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-1.13836e-06</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-1.13836e-06</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0.276864</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-9.80555e-07</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-9.80555e-07</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.277857</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1.02639e-06</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-1.02639e-06</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.277867</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-1.07361e-06</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-1.07361e-06</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-9.17633e-07</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-9.17633e-07</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.278866</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-9.53528e-07</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-9.53528e-07</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.278883</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.0068e-06</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-1.0068e-06</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="n">
+        <v>0.278882</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-8.46121e-07</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-8.46121e-07</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.279885</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-8.86689e-07</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-8.86689e-07</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.279898</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-9.3607e-07</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-9.3607e-07</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="n">
+        <v>0.279888</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-7.8726e-07</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-7.8726e-07</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.280897</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-8.15288e-07</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-8.15288e-07</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.280892</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-8.6478e-07</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-8.6478e-07</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-7.1617e-07</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-7.1617e-07</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.281902</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-7.55159e-07</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-7.55159e-07</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-7.99789e-07</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-7.99789e-07</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0.281891</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-6.56208e-07</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-6.56208e-07</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.282879</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-6.90412e-07</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-6.90412e-07</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.282886</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-7.31926e-07</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-7.31926e-07</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" t="n">
+        <v>0.282881</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-5.87722e-07</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-5.87722e-07</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.283879</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-6.28936e-07</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-6.28936e-07</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.283878</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-6.68314e-07</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-6.68314e-07</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" t="n">
+        <v>0.283882</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-5.26291e-07</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-5.26291e-07</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.284898</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-5.56434e-07</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-5.56434e-07</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.284895</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-6.01942e-07</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-6.01942e-07</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" t="n">
+        <v>0.284892</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-4.55235e-07</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-4.55235e-07</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.285894</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-4.90185e-07</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-4.90185e-07</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.285879</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-5.31621e-07</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-5.31621e-07</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" t="n">
+        <v>0.285878</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-3.96474e-07</v>
+      </c>
+      <c r="D66" t="n">
+        <v>-3.96474e-07</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.286879</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-4.23112e-07</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-4.23112e-07</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.286885</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-4.66751e-07</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-4.66751e-07</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" t="n">
+        <v>0.286873</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-3.28679e-07</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-3.28679e-07</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-3.6227e-07</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-3.6227e-07</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.287892</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-3.99935e-07</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-3.99935e-07</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" t="n">
+        <v>0.287883</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-2.71576e-07</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-2.71576e-07</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.288887</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-2.96411e-07</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-2.96411e-07</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.288886</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-3.42943e-07</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-3.42943e-07</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" t="n">
+        <v>0.288888</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-2.02511e-07</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-2.02511e-07</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.289879</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-2.34512e-07</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-2.34512e-07</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.289875</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-2.79776e-07</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-2.79776e-07</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.50471e-07</v>
+      </c>
+      <c r="D70" t="n">
+        <v>-1.50471e-07</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.290881</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-1.72113e-07</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-1.72113e-07</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.290876</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-2.20693e-07</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-2.20693e-07</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" t="n">
+        <v>0.290882</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-8.02499e-08</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-8.02499e-08</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.291888</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-1.15578e-07</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-1.15578e-07</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.291878</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-1.55011e-07</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-1.55011e-07</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" t="n">
+        <v>0.291898</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-2.2179e-08</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-2.2179e-08</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.292877</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-4.75148e-08</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-4.75148e-08</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.292871</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-9.54046e-08</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-9.54046e-08</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" t="n">
+        <v>0.292879</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4.98005e-08</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4.98005e-08</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.293878</v>
+      </c>
+      <c r="F73" t="n">
+        <v>7.529690000000001e-09</v>
+      </c>
+      <c r="G73" t="n">
+        <v>7.529690000000001e-09</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.293877</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-3.18371e-08</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-3.18371e-08</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" t="n">
+        <v>0.293883</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.07638e-07</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.07638e-07</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.294907</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6.90054e-08</v>
+      </c>
+      <c r="G74" t="n">
+        <v>6.90054e-08</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.294907</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2.59557e-08</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2.59557e-08</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" t="n">
+        <v>0.294909</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.75422e-07</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.75422e-07</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.31594e-07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.31594e-07</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.295906</v>
+      </c>
+      <c r="I75" t="n">
+        <v>9.473059999999999e-08</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9.473059999999999e-08</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" t="n">
+        <v>0.295919</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2.23613e-07</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2.23613e-07</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.296887</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.95351e-07</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.95351e-07</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.296896</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.48573e-07</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1.48573e-07</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" t="n">
+        <v>0.296901</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2.84766e-07</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2.84766e-07</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.297902</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.51363e-07</v>
+      </c>
+      <c r="G77" t="n">
+        <v>2.51363e-07</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.297903</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2.12586e-07</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.12586e-07</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" t="n">
+        <v>0.297906</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3.43526e-07</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3.43526e-07</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.298907</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3.19036e-07</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3.19036e-07</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.298904</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2.71725e-07</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.71725e-07</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0.2989</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4.0903e-07</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4.0903e-07</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.299888</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.74292e-07</v>
+      </c>
+      <c r="G79" t="n">
+        <v>3.74292e-07</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.299891</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3.33757e-07</v>
+      </c>
+      <c r="J79" t="n">
+        <v>3.33757e-07</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0.299896</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4.63596e-07</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4.63596e-07</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.298904</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-4.88504e-07</v>
+      </c>
+      <c r="G80" t="n">
+        <v>-4.88504e-07</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.298905</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-5.30542e-07</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-5.30542e-07</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-4.08091e-07</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-4.08091e-07</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.297902</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-7.41072e-07</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-7.41072e-07</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.297905</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-7.76189e-07</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-7.76189e-07</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0.297906</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-6.7114e-07</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-6.7114e-07</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.296889</v>
+      </c>
+      <c r="F82" t="n">
+        <v>-9.32843e-07</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-9.32843e-07</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.296906</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-9.646550000000001e-07</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-9.646550000000001e-07</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0.296895</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-8.64102e-07</v>
+      </c>
+      <c r="D83" t="n">
+        <v>-8.64102e-07</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.295903</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-1.09876e-06</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-1.09876e-06</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="I83" t="n">
+        <v>-1.1225e-06</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-1.1225e-06</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0.295917</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.03421e-06</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-1.03421e-06</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.294906</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-1.234e-06</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-1.234e-06</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-1.26937e-06</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-1.26937e-06</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0.294911</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.17158e-06</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1.17158e-06</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.293882</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1.36562e-06</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-1.36562e-06</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.293893</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-1.39582e-06</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-1.39582e-06</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0.293889</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.31075e-06</v>
+      </c>
+      <c r="D86" t="n">
+        <v>-1.31075e-06</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.292897</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-1.482e-06</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-1.482e-06</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.292882</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-1.51391e-06</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-1.51391e-06</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0.292886</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.42059e-06</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-1.42059e-06</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.291901</v>
+      </c>
+      <c r="F87" t="n">
+        <v>-1.59849e-06</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-1.59849e-06</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.291888</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-1.61955e-06</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-1.61955e-06</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0.291904</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.53671e-06</v>
+      </c>
+      <c r="D88" t="n">
+        <v>-1.53671e-06</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.290883</v>
+      </c>
+      <c r="F88" t="n">
+        <v>-1.69615e-06</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-1.69615e-06</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.290881</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-1.72565e-06</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-1.72565e-06</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0.290885</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.63382e-06</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-1.63382e-06</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.289871</v>
+      </c>
+      <c r="F89" t="n">
+        <v>-1.79986e-06</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-1.79986e-06</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.289885</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-1.8235e-06</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-1.8235e-06</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0.289884</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.74431e-06</v>
+      </c>
+      <c r="D90" t="n">
+        <v>-1.74431e-06</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.288876</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-1.89063e-06</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-1.89063e-06</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.288899</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-1.91453e-06</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-1.91453e-06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0.288891</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-1.83165e-06</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-1.83165e-06</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.287885</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-1.98392e-06</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-1.98392e-06</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.287896</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-2.00149e-06</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-2.00149e-06</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0.287889</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.93227e-06</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-1.93227e-06</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.286887</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-2.06859e-06</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-2.06859e-06</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.286888</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-2.08759e-06</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-2.08759e-06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0.286883</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-2.01368e-06</v>
+      </c>
+      <c r="D93" t="n">
+        <v>-2.01368e-06</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-2.15379e-06</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-2.15379e-06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.285888</v>
+      </c>
+      <c r="I93" t="n">
+        <v>-2.17135e-06</v>
+      </c>
+      <c r="J93" t="n">
+        <v>-2.17135e-06</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0.285888</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-2.10544e-06</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-2.10544e-06</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.284894</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-2.23169e-06</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-2.23169e-06</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.284908</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-2.25659e-06</v>
+      </c>
+      <c r="J94" t="n">
+        <v>-2.25659e-06</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0.284894</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-2.18019e-06</v>
+      </c>
+      <c r="D95" t="n">
+        <v>-2.18019e-06</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.283891</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-2.31403e-06</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-2.31403e-06</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.283896</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-2.33589e-06</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-2.33589e-06</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0.283894</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-2.26953e-06</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-2.26953e-06</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.282892</v>
+      </c>
+      <c r="F96" t="n">
+        <v>-2.39654e-06</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-2.39654e-06</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.282889</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-2.42122e-06</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-2.42122e-06</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-2.34243e-06</v>
+      </c>
+      <c r="D97" t="n">
+        <v>-2.34243e-06</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.281912</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-2.47919e-06</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-2.47919e-06</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.281905</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-2.49866e-06</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-2.49866e-06</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0.281913</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-2.42224e-06</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-2.42224e-06</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.280898</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-2.55335e-06</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-2.55335e-06</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.280892</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-2.57819e-06</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-2.57819e-06</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0.280895</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-2.48515e-06</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-2.48515e-06</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.279896</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-2.63067e-06</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-2.63067e-06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.279888</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-2.65048e-06</v>
+      </c>
+      <c r="J99" t="n">
+        <v>-2.65048e-06</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.279897</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.57244e-06</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-2.57244e-06</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.278884</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-2.70081e-06</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-2.70081e-06</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.278885</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-2.72881e-06</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-2.72881e-06</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.278892</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-2.63978e-06</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-2.63978e-06</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.277876</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-2.77851e-06</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-2.77851e-06</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.277873</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-2.80206e-06</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-2.80206e-06</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0.277876</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-2.72565e-06</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-2.72565e-06</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.276883</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-2.84882e-06</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-2.84882e-06</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.276879</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-2.87577e-06</v>
+      </c>
+      <c r="J102" t="n">
+        <v>-2.87577e-06</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" t="n">
+        <v>0.276888</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-2.78948e-06</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-2.78948e-06</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.275887</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-2.92478e-06</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-2.92478e-06</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-2.94669e-06</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-2.94669e-06</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" t="n">
+        <v>0.275883</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-2.87387e-06</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-2.87387e-06</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.274876</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-2.99594e-06</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-2.99594e-06</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.274876</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-3.02143e-06</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-3.02143e-06</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" t="n">
+        <v>0.274877</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2.93966e-06</v>
+      </c>
+      <c r="D105" t="n">
+        <v>-2.93966e-06</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.273883</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-3.0704e-06</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-3.0704e-06</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.273875</v>
+      </c>
+      <c r="I105" t="n">
+        <v>-3.09117e-06</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-3.09117e-06</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" t="n">
+        <v>0.273875</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-3.02223e-06</v>
+      </c>
+      <c r="D106" t="n">
+        <v>-3.02223e-06</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.272894</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-3.14035e-06</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-3.14035e-06</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.272891</v>
+      </c>
+      <c r="I106" t="n">
+        <v>-3.16758e-06</v>
+      </c>
+      <c r="J106" t="n">
+        <v>-3.16758e-06</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" t="n">
+        <v>0.272887</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-3.09276e-06</v>
+      </c>
+      <c r="D107" t="n">
+        <v>-3.09276e-06</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.271895</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-3.21271e-06</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-3.21271e-06</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.271892</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-3.23536e-06</v>
+      </c>
+      <c r="J107" t="n">
+        <v>-3.23536e-06</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" t="n">
+        <v>0.271887</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-3.17078e-06</v>
+      </c>
+      <c r="D108" t="n">
+        <v>-3.17078e-06</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.270877</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-3.27967e-06</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-3.27967e-06</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.270878</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-3.3077e-06</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-3.3077e-06</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" t="n">
+        <v>0.270878</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-3.23527e-06</v>
+      </c>
+      <c r="D109" t="n">
+        <v>-3.23527e-06</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.269892</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-3.35427e-06</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-3.35427e-06</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.269897</v>
+      </c>
+      <c r="I109" t="n">
+        <v>-3.37634e-06</v>
+      </c>
+      <c r="J109" t="n">
+        <v>-3.37634e-06</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" t="n">
+        <v>0.269885</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-3.31005e-06</v>
+      </c>
+      <c r="D110" t="n">
+        <v>-3.31005e-06</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.268899</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-3.42621e-06</v>
+      </c>
+      <c r="G110" t="n">
+        <v>-3.42621e-06</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.268898</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-3.44843e-06</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-3.44843e-06</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" t="n">
+        <v>0.268884</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-3.37439e-06</v>
+      </c>
+      <c r="D111" t="n">
+        <v>-3.37439e-06</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.267879</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-3.50069e-06</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-3.50069e-06</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.267879</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-3.51528e-06</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-3.51528e-06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" t="n">
+        <v>0.267863</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-3.44998e-06</v>
+      </c>
+      <c r="D112" t="n">
+        <v>-3.44998e-06</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.266887</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-3.57038e-06</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-3.57038e-06</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.266878</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-3.59032e-06</v>
+      </c>
+      <c r="J112" t="n">
+        <v>-3.59032e-06</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" t="n">
+        <v>0.266864</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-3.51772e-06</v>
+      </c>
+      <c r="D113" t="n">
+        <v>-3.51772e-06</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.265898</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-3.64496e-06</v>
+      </c>
+      <c r="G113" t="n">
+        <v>-3.64496e-06</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.265895</v>
+      </c>
+      <c r="I113" t="n">
+        <v>-3.66047e-06</v>
+      </c>
+      <c r="J113" t="n">
+        <v>-3.66047e-06</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" t="n">
+        <v>0.265873</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-3.60224e-06</v>
+      </c>
+      <c r="D114" t="n">
+        <v>-3.60224e-06</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.264887</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-3.71291e-06</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-3.71291e-06</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.264887</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-3.74249e-06</v>
+      </c>
+      <c r="J114" t="n">
+        <v>-3.74249e-06</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" t="n">
+        <v>0.264872</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-3.66642e-06</v>
+      </c>
+      <c r="D115" t="n">
+        <v>-3.66642e-06</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-3.79474e-06</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-3.79474e-06</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.263892</v>
+      </c>
+      <c r="I115" t="n">
+        <v>-3.81326e-06</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-3.81326e-06</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" t="n">
+        <v>0.263868</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-3.74383e-06</v>
+      </c>
+      <c r="D116" t="n">
+        <v>-3.74383e-06</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.262892</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-3.86601e-06</v>
+      </c>
+      <c r="G116" t="n">
+        <v>-3.86601e-06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.262904</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-3.89119e-06</v>
+      </c>
+      <c r="J116" t="n">
+        <v>-3.89119e-06</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.262878</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-3.81417e-06</v>
+      </c>
+      <c r="D117" t="n">
+        <v>-3.81417e-06</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.261899</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-3.93466e-06</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-3.93466e-06</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.261904</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-3.9573e-06</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-3.9573e-06</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.261889</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-3.8899e-06</v>
+      </c>
+      <c r="D118" t="n">
+        <v>-3.8899e-06</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.260901</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-4.00953e-06</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-4.00953e-06</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.260893</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-4.03698e-06</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-4.03698e-06</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.260892</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-3.96239e-06</v>
+      </c>
+      <c r="D119" t="n">
+        <v>-3.96239e-06</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.259899</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-4.0876e-06</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-4.0876e-06</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.259898</v>
+      </c>
+      <c r="I119" t="n">
+        <v>-4.11138e-06</v>
+      </c>
+      <c r="J119" t="n">
+        <v>-4.11138e-06</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.259887</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-4.04751e-06</v>
+      </c>
+      <c r="D120" t="n">
+        <v>-4.04751e-06</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.258893</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-4.15772e-06</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-4.15772e-06</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.258897</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-4.19017e-06</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-4.19017e-06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-4.11317e-06</v>
+      </c>
+      <c r="D121" t="n">
+        <v>-4.11317e-06</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.257895</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-4.23724e-06</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-4.23724e-06</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.257896</v>
+      </c>
+      <c r="I121" t="n">
+        <v>-4.26656e-06</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-4.26656e-06</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.257888</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-4.19594e-06</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-4.19594e-06</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.256888</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-4.31036e-06</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-4.31036e-06</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.256898</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-4.34308e-06</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-4.34308e-06</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.256898</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-4.26938e-06</v>
+      </c>
+      <c r="D123" t="n">
+        <v>-4.26938e-06</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.255905</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-4.38963e-06</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-4.38963e-06</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.255925</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-4.41716e-06</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-4.41716e-06</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.255919</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-4.34888e-06</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-4.34888e-06</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.254889</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-4.4709e-06</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-4.4709e-06</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.254897</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-4.50134e-06</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-4.50134e-06</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.254899</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-4.42342e-06</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-4.42342e-06</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.253896</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-4.55811e-06</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-4.55811e-06</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.253913</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-4.58172e-06</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-4.58172e-06</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.253906</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-4.51668e-06</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-4.51668e-06</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-4.63655e-06</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-4.63655e-06</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-4.66074e-06</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-4.66074e-06</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.252903</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-4.59447e-06</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-4.59447e-06</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.251866</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-4.7194e-06</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-4.7194e-06</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.251877</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-4.74096e-06</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-4.74096e-06</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.251875</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-4.67575e-06</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-4.67575e-06</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-4.80342e-06</v>
+      </c>
+      <c r="G128" t="n">
+        <v>-4.80342e-06</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.250882</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-4.82348e-06</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-4.82348e-06</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.250888</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-4.75186e-06</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-4.75186e-06</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.249876</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-4.88872e-06</v>
+      </c>
+      <c r="G129" t="n">
+        <v>-4.88872e-06</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.249885</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-4.9074e-06</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-4.9074e-06</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.249881</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-4.84572e-06</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-4.84572e-06</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.248869</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-4.97031e-06</v>
+      </c>
+      <c r="G130" t="n">
+        <v>-4.97031e-06</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.248881</v>
+      </c>
+      <c r="I130" t="n">
+        <v>-5.00377e-06</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-5.00377e-06</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.248876</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-4.927e-06</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-4.927e-06</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.247872</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-5.06299e-06</v>
+      </c>
+      <c r="G131" t="n">
+        <v>-5.06299e-06</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.247886</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-5.08775e-06</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-5.08775e-06</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.247872</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-5.02801e-06</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-5.02801e-06</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.246877</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-5.15188e-06</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-5.15188e-06</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.246884</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-5.17678e-06</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-5.17678e-06</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.246876</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-5.10312e-06</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-5.10312e-06</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.245872</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-5.24103e-06</v>
+      </c>
+      <c r="G133" t="n">
+        <v>-5.24103e-06</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.245887</v>
+      </c>
+      <c r="I133" t="n">
+        <v>-5.26088e-06</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-5.26088e-06</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.245881</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-5.19816e-06</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-5.19816e-06</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.244875</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-5.32887e-06</v>
+      </c>
+      <c r="G134" t="n">
+        <v>-5.32887e-06</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.24489</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-5.3552e-06</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-5.3552e-06</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.244886</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-5.27716e-06</v>
+      </c>
+      <c r="D135" t="n">
+        <v>-5.27716e-06</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.243893</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-5.41771e-06</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-5.41771e-06</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.243887</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-5.44666e-06</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-5.44666e-06</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.243901</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-5.37836e-06</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-5.37836e-06</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.242882</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-5.51067e-06</v>
+      </c>
+      <c r="G136" t="n">
+        <v>-5.51067e-06</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.242879</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-5.53784e-06</v>
+      </c>
+      <c r="J136" t="n">
+        <v>-5.53784e-06</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.242895</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-5.46685e-06</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-5.46685e-06</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.241866</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-5.6077e-06</v>
+      </c>
+      <c r="G137" t="n">
+        <v>-5.6077e-06</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.241871</v>
+      </c>
+      <c r="I137" t="n">
+        <v>-5.63048e-06</v>
+      </c>
+      <c r="J137" t="n">
+        <v>-5.63048e-06</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.241877</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-5.56301e-06</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-5.56301e-06</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.240875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-5.69747e-06</v>
+      </c>
+      <c r="G138" t="n">
+        <v>-5.69747e-06</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.240874</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-5.72804e-06</v>
+      </c>
+      <c r="J138" t="n">
+        <v>-5.72804e-06</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.240881</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-5.64996e-06</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-5.64996e-06</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.239888</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-5.79657e-06</v>
+      </c>
+      <c r="G139" t="n">
+        <v>-5.79657e-06</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.239886</v>
+      </c>
+      <c r="I139" t="n">
+        <v>-5.81948e-06</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-5.81948e-06</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.23989</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-5.75423e-06</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-5.75423e-06</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.238883</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-5.89253e-06</v>
+      </c>
+      <c r="G140" t="n">
+        <v>-5.89253e-06</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.238881</v>
+      </c>
+      <c r="I140" t="n">
+        <v>-5.92511e-06</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-5.92511e-06</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.238886</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-5.84579e-06</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-5.84579e-06</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.237887</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-5.99665e-06</v>
+      </c>
+      <c r="G141" t="n">
+        <v>-5.99665e-06</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.237887</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-6.02595e-06</v>
+      </c>
+      <c r="J141" t="n">
+        <v>-6.02595e-06</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.237889</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-5.95287e-06</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-5.95287e-06</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.236899</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-6.10236e-06</v>
+      </c>
+      <c r="G142" t="n">
+        <v>-6.10236e-06</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.236897</v>
+      </c>
+      <c r="I142" t="n">
+        <v>-6.12995e-06</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-6.12995e-06</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.236901</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-6.04634e-06</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-6.04634e-06</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.235893</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-6.20655e-06</v>
+      </c>
+      <c r="G143" t="n">
+        <v>-6.20655e-06</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.235891</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-6.23009e-06</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-6.23009e-06</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144" t="n">
+        <v>0.235898</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-6.16104e-06</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-6.16104e-06</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.234892</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-6.3131e-06</v>
+      </c>
+      <c r="G144" t="n">
+        <v>-6.3131e-06</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.234888</v>
+      </c>
+      <c r="I144" t="n">
+        <v>-6.33597e-06</v>
+      </c>
+      <c r="J144" t="n">
+        <v>-6.33597e-06</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.234889</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-6.26322e-06</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-6.26322e-06</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.233885</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-6.41917e-06</v>
+      </c>
+      <c r="G145" t="n">
+        <v>-6.41917e-06</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.233889</v>
+      </c>
+      <c r="I145" t="n">
+        <v>-6.43842e-06</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-6.43842e-06</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.233874</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-6.37307e-06</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-6.37307e-06</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.23289</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-6.52501e-06</v>
+      </c>
+      <c r="G146" t="n">
+        <v>-6.52501e-06</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.232887</v>
+      </c>
+      <c r="I146" t="n">
+        <v>-6.5506e-06</v>
+      </c>
+      <c r="J146" t="n">
+        <v>-6.5506e-06</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.232884</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-6.46865e-06</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-6.46865e-06</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.231875</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-6.63851e-06</v>
+      </c>
+      <c r="G147" t="n">
+        <v>-6.63851e-06</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.231894</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-6.65614e-06</v>
+      </c>
+      <c r="J147" t="n">
+        <v>-6.65614e-06</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.231873</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-6.58769e-06</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-6.58769e-06</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.230877</v>
+      </c>
+      <c r="F148" t="n">
+        <v>-6.74799e-06</v>
+      </c>
+      <c r="G148" t="n">
+        <v>-6.74799e-06</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.230889</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-6.77316e-06</v>
+      </c>
+      <c r="J148" t="n">
+        <v>-6.77316e-06</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.230873</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-6.69497e-06</v>
+      </c>
+      <c r="D149" t="n">
+        <v>-6.69497e-06</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.229873</v>
+      </c>
+      <c r="F149" t="n">
+        <v>-6.86313e-06</v>
+      </c>
+      <c r="G149" t="n">
+        <v>-6.86313e-06</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.229875</v>
+      </c>
+      <c r="I149" t="n">
+        <v>-6.87909e-06</v>
+      </c>
+      <c r="J149" t="n">
+        <v>-6.87909e-06</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.229864</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-6.81075e-06</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-6.81075e-06</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.228882</v>
+      </c>
+      <c r="F150" t="n">
+        <v>-6.97676e-06</v>
+      </c>
+      <c r="G150" t="n">
+        <v>-6.97676e-06</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.228881</v>
+      </c>
+      <c r="I150" t="n">
+        <v>-7.00186e-06</v>
+      </c>
+      <c r="J150" t="n">
+        <v>-7.00186e-06</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.228878</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-6.91934e-06</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-6.91934e-06</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.227891</v>
+      </c>
+      <c r="F151" t="n">
+        <v>-7.09677e-06</v>
+      </c>
+      <c r="G151" t="n">
+        <v>-7.09677e-06</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.227894</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-7.12096e-06</v>
+      </c>
+      <c r="J151" t="n">
+        <v>-7.12096e-06</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.227882</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-7.04261e-06</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-7.04261e-06</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.226871</v>
+      </c>
+      <c r="F152" t="n">
+        <v>-7.21844e-06</v>
+      </c>
+      <c r="G152" t="n">
+        <v>-7.21844e-06</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.226858</v>
+      </c>
+      <c r="I152" t="n">
+        <v>-7.2461e-06</v>
+      </c>
+      <c r="J152" t="n">
+        <v>-7.2461e-06</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.226862</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-7.15882e-06</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-7.15882e-06</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.225869</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-7.33606e-06</v>
+      </c>
+      <c r="G153" t="n">
+        <v>-7.33606e-06</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.225857</v>
+      </c>
+      <c r="I153" t="n">
+        <v>-7.36487e-06</v>
+      </c>
+      <c r="J153" t="n">
+        <v>-7.36487e-06</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.225858</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-7.28949e-06</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-7.28949e-06</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.224872</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-7.45773e-06</v>
+      </c>
+      <c r="G154" t="n">
+        <v>-7.45773e-06</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.224865</v>
+      </c>
+      <c r="I154" t="n">
+        <v>-7.48899e-06</v>
+      </c>
+      <c r="J154" t="n">
+        <v>-7.48899e-06</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.224863</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-7.40298e-06</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-7.40298e-06</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
